--- a/portfolio_aom_analysis_report.xlsx
+++ b/portfolio_aom_analysis_report.xlsx
@@ -511,7 +511,7 @@
         <v>-3.069466882067858</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -553,16 +553,16 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C5" t="n">
         <v>57.68</v>
-      </c>
-      <c r="C5" t="n">
-        <v>45.5</v>
       </c>
       <c r="D5" t="n">
         <v>45.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-21.11650485436893</v>
       </c>
       <c r="F5" t="n">
         <v>20</v>

--- a/portfolio_aom_analysis_report.xlsx
+++ b/portfolio_aom_analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,10 +478,10 @@
         <v>2.13</v>
       </c>
       <c r="D2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="E2" t="n">
-        <v>-39.43661971830986</v>
+        <v>-39.90610328638497</v>
       </c>
       <c r="F2" t="n">
         <v>46</v>
@@ -505,13 +505,13 @@
         <v>6.19</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.069466882067858</v>
+        <v>-6.300484652665599</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -532,10 +532,10 @@
         <v>20.98</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-9.437559580552909</v>
+        <v>-10.3908484270734</v>
       </c>
       <c r="F4" t="n">
         <v>48</v>
@@ -559,13 +559,13 @@
         <v>57.68</v>
       </c>
       <c r="D5" t="n">
-        <v>45.5</v>
+        <v>47.25</v>
       </c>
       <c r="E5" t="n">
-        <v>-21.11650485436893</v>
+        <v>-18.08252427184466</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         <v>39.62</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-59.61635537607268</v>
+        <v>-59.86875315497223</v>
       </c>
       <c r="F6" t="n">
         <v>46</v>
@@ -613,10 +613,10 @@
         <v>23.05</v>
       </c>
       <c r="D7" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.459869848156179</v>
+        <v>-10.19522776572669</v>
       </c>
       <c r="F7" t="n">
         <v>58</v>
@@ -640,10 +640,10 @@
         <v>32.8</v>
       </c>
       <c r="D8" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="E8" t="n">
-        <v>-41.46341463414634</v>
+        <v>-40.24390243902438</v>
       </c>
       <c r="F8" t="n">
         <v>30</v>
@@ -667,10 +667,10 @@
         <v>10.22</v>
       </c>
       <c r="D9" t="n">
-        <v>35.5</v>
+        <v>35.25</v>
       </c>
       <c r="E9" t="n">
-        <v>247.3581213307241</v>
+        <v>244.9119373776908</v>
       </c>
       <c r="F9" t="n">
         <v>60</v>
@@ -694,10 +694,10 @@
         <v>7.26</v>
       </c>
       <c r="D10" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="E10" t="n">
-        <v>-47.93388429752066</v>
+        <v>-47.65840220385675</v>
       </c>
       <c r="F10" t="n">
         <v>54</v>
@@ -721,10 +721,10 @@
         <v>21.73</v>
       </c>
       <c r="D11" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="n">
-        <v>-40.63506672802577</v>
+        <v>-42.47583985273815</v>
       </c>
       <c r="F11" t="n">
         <v>54</v>
@@ -775,10 +775,10 @@
         <v>18.76</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="E13" t="n">
-        <v>-40.8315565031983</v>
+        <v>-42.43070362473348</v>
       </c>
       <c r="F13" t="n">
         <v>54</v>
@@ -802,10 +802,10 @@
         <v>28.87</v>
       </c>
       <c r="D14" t="n">
-        <v>15.4</v>
+        <v>14.9</v>
       </c>
       <c r="E14" t="n">
-        <v>-46.65742985798407</v>
+        <v>-48.3893314859716</v>
       </c>
       <c r="F14" t="n">
         <v>68</v>
@@ -840,6 +840,33 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>✅ ซื้อเพิ่ม</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HMPRO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>200</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6441223832528187</v>
+      </c>
+      <c r="F16" t="n">
+        <v>74</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>📦 ถือต่อ</t>
         </is>
       </c>
     </row>

--- a/portfolio_aom_analysis_report.xlsx
+++ b/portfolio_aom_analysis_report.xlsx
@@ -1568,7 +1568,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Accumulate</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Accumulate</t>
         </is>
       </c>
       <c r="O18" t="n">

--- a/portfolio_aom_analysis_report.xlsx
+++ b/portfolio_aom_analysis_report.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,16 @@
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,72 +488,122 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Trend_Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Entry_Zone</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Exit_Zone</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Stop_Loss</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Upside_Pct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>RRR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Cost_Value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Market_Value</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>High_52W</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Low_52W</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Gain_Loss_Value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Gain_Loss_Pct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Price_Position</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Gain_Loss_Value</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Gain_Loss_Pct</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Total_Score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Advice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Target_Action</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_Ratio</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Entry_Zone_Low</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Entry_Zone_High</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Exit_Zone_Low</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Exit_Zone_High</t>
         </is>
       </c>
     </row>
@@ -567,49 +627,87 @@
       <c r="E2" t="n">
         <v>1.28</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.25 - 1.31</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.31 - 1.35</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.304687500000006</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3189189189189197</v>
+      </c>
+      <c r="L2" t="n">
         <v>1065</v>
       </c>
-      <c r="G2" t="n">
+      <c r="M2" t="n">
         <v>640</v>
       </c>
-      <c r="H2" t="n">
+      <c r="N2" t="n">
+        <v>-425</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-39.90610328638497</v>
+      </c>
+      <c r="P2" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>60</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6505659032171821</v>
+      </c>
+      <c r="U2" t="n">
+        <v>16</v>
+      </c>
+      <c r="V2" t="n">
+        <v>78</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.3095</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.35</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-425</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-39.90610328638497</v>
-      </c>
-      <c r="M2" t="n">
-        <v>60</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>16</v>
-      </c>
-      <c r="P2" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.4997</v>
-      </c>
-      <c r="S2" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -632,49 +730,87 @@
       <c r="E3" t="n">
         <v>5.55</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4.00 - 4.20</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6.30 - 6.50</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.6036036036036</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4314285714285714</v>
+      </c>
+      <c r="L3" t="n">
         <v>1238</v>
       </c>
-      <c r="G3" t="n">
+      <c r="M3" t="n">
         <v>1110</v>
       </c>
-      <c r="H3" t="n">
+      <c r="N3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-10.33925686591277</v>
+      </c>
+      <c r="P3" t="n">
+        <v>61.99999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5167883201677864</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.53247</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>38.44847539454688</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.305</v>
+      </c>
+      <c r="AC3" t="n">
         <v>6.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>61.99999999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-10.33925686591277</v>
-      </c>
-      <c r="M3" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.53247</v>
-      </c>
-      <c r="S3" t="n">
-        <v>38.44847539454688</v>
       </c>
     </row>
     <row r="4">
@@ -697,49 +833,87 @@
       <c r="E4" t="n">
         <v>18.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>17.40 - 18.27</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>24.15 - 24.90</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.55675675675675</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.869543147208117</v>
+      </c>
+      <c r="L4" t="n">
         <v>25176</v>
       </c>
-      <c r="G4" t="n">
+      <c r="M4" t="n">
         <v>22200</v>
       </c>
-      <c r="H4" t="n">
+      <c r="N4" t="n">
+        <v>-2976</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-11.82078169685415</v>
+      </c>
+      <c r="P4" t="n">
+        <v>14.66666666666669</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>65.53333333333333</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7667686188704068</v>
+      </c>
+      <c r="U4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>15.302</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>40.00005086250086</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>24.153</v>
+      </c>
+      <c r="AC4" t="n">
         <v>24.9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14.66666666666669</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-2976</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-11.82078169685415</v>
-      </c>
-      <c r="M4" t="n">
-        <v>65.53333333333333</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15.302</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.15896</v>
-      </c>
-      <c r="S4" t="n">
-        <v>40.00005086250086</v>
       </c>
     </row>
     <row r="5">
@@ -762,49 +936,87 @@
       <c r="E5" t="n">
         <v>44.75</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>40.50 - 42.52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>52.87 - 54.50</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>38.475</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.13407821229051</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.293227091633467</v>
+      </c>
+      <c r="L5" t="n">
         <v>17304</v>
       </c>
-      <c r="G5" t="n">
+      <c r="M5" t="n">
         <v>13425</v>
       </c>
-      <c r="H5" t="n">
+      <c r="N5" t="n">
+        <v>-3879</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-22.41678224687933</v>
+      </c>
+      <c r="P5" t="n">
+        <v>30.35714285714285</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>57.96428571428572</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0.6196314228960125</v>
+      </c>
+      <c r="U5" t="n">
+        <v>14.435484</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="W5" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.33418</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>44.82758620689656</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>42.525</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>52.865</v>
+      </c>
+      <c r="AC5" t="n">
         <v>54.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30.35714285714285</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-3879</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-22.41678224687933</v>
-      </c>
-      <c r="M5" t="n">
-        <v>57.96428571428572</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>14.435484</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33418</v>
-      </c>
-      <c r="S5" t="n">
-        <v>44.82758620689656</v>
       </c>
     </row>
     <row r="6">
@@ -827,49 +1039,87 @@
       <c r="E6" t="n">
         <v>14.7</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>13.90 - 14.60</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25.22 - 26.00</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>13.205</v>
+      </c>
+      <c r="J6" t="n">
+        <v>71.56462585034014</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.036789297658866</v>
+      </c>
+      <c r="L6" t="n">
         <v>31220.56</v>
       </c>
-      <c r="G6" t="n">
+      <c r="M6" t="n">
         <v>11583.6</v>
       </c>
-      <c r="H6" t="n">
+      <c r="N6" t="n">
+        <v>-19636.96</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-62.89752650176679</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.611570247933876</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>60.33884297520661</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4781806021347391</v>
+      </c>
+      <c r="U6" t="n">
+        <v>16.333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.1140001</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.57284</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>37.92170292856077</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>14.595</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AC6" t="n">
         <v>26</v>
-      </c>
-      <c r="I6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.611570247933876</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-19636.96</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-62.89752650176679</v>
-      </c>
-      <c r="M6" t="n">
-        <v>60.33884297520661</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>16.333334</v>
-      </c>
-      <c r="P6" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.1140001</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.57284</v>
-      </c>
-      <c r="S6" t="n">
-        <v>37.92170292856077</v>
       </c>
     </row>
     <row r="7">
@@ -892,49 +1142,87 @@
       <c r="E7" t="n">
         <v>19.2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>18.10 - 19.01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>25.70 - 26.50</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>17.195</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33.88020833333333</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.244389027431422</v>
+      </c>
+      <c r="L7" t="n">
         <v>31892</v>
       </c>
-      <c r="G7" t="n">
+      <c r="M7" t="n">
         <v>26880</v>
       </c>
-      <c r="H7" t="n">
+      <c r="N7" t="n">
+        <v>-5012</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-15.71553994732222</v>
+      </c>
+      <c r="P7" t="n">
+        <v>13.09523809523807</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>65.19047619047619</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>1.09724800305792</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6.1538467</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>10.5100006</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.05188</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>15.99999694823985</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>19.005</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25.705</v>
+      </c>
+      <c r="AC7" t="n">
         <v>26.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>13.09523809523807</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-5012</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-15.71553994732222</v>
-      </c>
-      <c r="M7" t="n">
-        <v>65.19047619047619</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>6.1538467</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>10.5100006</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.05188</v>
-      </c>
-      <c r="S7" t="n">
-        <v>15.99999694823985</v>
       </c>
     </row>
     <row r="8">
@@ -957,49 +1245,87 @@
       <c r="E8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15.80 - 16.59</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>24.49 - 25.25</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.68010752688171</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.641364902506963</v>
+      </c>
+      <c r="L8" t="n">
         <v>3280</v>
       </c>
-      <c r="G8" t="n">
+      <c r="M8" t="n">
         <v>1860</v>
       </c>
-      <c r="H8" t="n">
+      <c r="N8" t="n">
+        <v>-1419.999999999999</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-43.29268292682926</v>
+      </c>
+      <c r="P8" t="n">
+        <v>29.62962962962964</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>46.03703703703704</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8269922682385363</v>
+      </c>
+      <c r="U8" t="n">
+        <v>16.607143</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W8" t="n">
+        <v>10.017</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.54054</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>64.62050676638384</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.4925</v>
+      </c>
+      <c r="AC8" t="n">
         <v>25.25</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>29.62962962962964</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-1419.999999999999</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-43.29268292682926</v>
-      </c>
-      <c r="M8" t="n">
-        <v>46.03703703703704</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>16.607143</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10.017</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.54054</v>
-      </c>
-      <c r="S8" t="n">
-        <v>64.62050676638384</v>
       </c>
     </row>
     <row r="9">
@@ -1022,49 +1348,87 @@
       <c r="E9" t="n">
         <v>32.25</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>20.80 - 21.84</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>34.92 - 36.00</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.279069767441866</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2137710168134509</v>
+      </c>
+      <c r="L9" t="n">
         <v>7154</v>
       </c>
-      <c r="G9" t="n">
+      <c r="M9" t="n">
         <v>22575</v>
       </c>
-      <c r="H9" t="n">
+      <c r="N9" t="n">
+        <v>15421</v>
+      </c>
+      <c r="O9" t="n">
+        <v>215.5577299412916</v>
+      </c>
+      <c r="P9" t="n">
+        <v>75.32894736842105</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>75.96710526315789</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4611459049472842</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9.347826</v>
+      </c>
+      <c r="V9" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="W9" t="n">
+        <v>10.986</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>45.15809304913206</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="AC9" t="n">
         <v>36</v>
-      </c>
-      <c r="I9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>75.32894736842105</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15421</v>
-      </c>
-      <c r="L9" t="n">
-        <v>215.5577299412916</v>
-      </c>
-      <c r="M9" t="n">
-        <v>75.96710526315789</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>9.347826</v>
-      </c>
-      <c r="P9" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10.986</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>45.15809304913206</v>
       </c>
     </row>
     <row r="10">
@@ -1087,49 +1451,87 @@
       <c r="E10" t="n">
         <v>3.78</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.18 - 3.34</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.37 - 4.50</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15.47619047619049</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7707509881422931</v>
+      </c>
+      <c r="L10" t="n">
         <v>2178</v>
       </c>
-      <c r="G10" t="n">
+      <c r="M10" t="n">
         <v>1134</v>
       </c>
-      <c r="H10" t="n">
+      <c r="N10" t="n">
+        <v>-1044</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-47.93388429752066</v>
+      </c>
+      <c r="P10" t="n">
+        <v>45.45454545454543</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>44.45454545454545</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Reduce/Cut</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Reduce 50%</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>0.5814084071891462</v>
+      </c>
+      <c r="U10" t="n">
+        <v>12.193548</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.51037</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>51.72413793103448</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.339</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.365</v>
+      </c>
+      <c r="AC10" t="n">
         <v>4.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="J10" t="n">
-        <v>45.45454545454543</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-1044</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-47.93388429752066</v>
-      </c>
-      <c r="M10" t="n">
-        <v>44.45454545454545</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Reduce/Cut</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>12.193548</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.51037</v>
-      </c>
-      <c r="S10" t="n">
-        <v>51.72413793103448</v>
       </c>
     </row>
     <row r="11">
@@ -1152,49 +1554,87 @@
       <c r="E11" t="n">
         <v>11.9</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10.10 - 10.61</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>15.13 - 15.60</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.594999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27.15966386554621</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.402169197396962</v>
+      </c>
+      <c r="L11" t="n">
         <v>41287</v>
       </c>
-      <c r="G11" t="n">
+      <c r="M11" t="n">
         <v>22610</v>
       </c>
-      <c r="H11" t="n">
+      <c r="N11" t="n">
+        <v>-18677</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-45.23699953980672</v>
+      </c>
+      <c r="P11" t="n">
+        <v>32.72727272727274</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>72.72727272727272</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 10.61</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0.5288999986035275</v>
+      </c>
+      <c r="U11" t="n">
+        <v>12.6595745</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10.147</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.20703</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>29.99997456866872</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>10.605</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>15.132</v>
+      </c>
+      <c r="AC11" t="n">
         <v>15.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>32.72727272727274</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-18677</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-45.23699953980672</v>
-      </c>
-      <c r="M11" t="n">
-        <v>72.72727272727272</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>12.6595745</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10.147</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.20703</v>
-      </c>
-      <c r="S11" t="n">
-        <v>29.99997456866872</v>
       </c>
     </row>
     <row r="12">
@@ -1217,49 +1657,87 @@
       <c r="E12" t="n">
         <v>1.42</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bullish 📈</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.15 - 1.21</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.50 - 1.55</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.0925</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.880281690140855</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.254961832061069</v>
+      </c>
+      <c r="L12" t="n">
         <v>5502</v>
       </c>
-      <c r="G12" t="n">
+      <c r="M12" t="n">
         <v>2982</v>
       </c>
-      <c r="H12" t="n">
+      <c r="N12" t="n">
+        <v>-2520</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-45.80152671755726</v>
+      </c>
+      <c r="P12" t="n">
+        <v>67.49999999999999</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2144821053118</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8.875</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5.804</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.2075</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.5035</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J12" t="n">
-        <v>67.49999999999999</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-2520</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-45.80152671755726</v>
-      </c>
-      <c r="M12" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>8.875</v>
-      </c>
-      <c r="P12" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.804</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.29902</v>
-      </c>
-      <c r="S12" t="n">
-        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="13">
@@ -1282,49 +1760,87 @@
       <c r="E13" t="n">
         <v>10.1</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5.10 - 5.35</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>11.06 - 11.40</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.845</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9.485148514851486</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.182302568981922</v>
+      </c>
+      <c r="L13" t="n">
         <v>18760</v>
       </c>
-      <c r="G13" t="n">
+      <c r="M13" t="n">
         <v>10100</v>
       </c>
-      <c r="H13" t="n">
+      <c r="N13" t="n">
+        <v>-8660</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-46.16204690831557</v>
+      </c>
+      <c r="P13" t="n">
+        <v>79.36507936507937</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>72.56349206349206</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 5.35</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6275624959835486</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.287</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.12099</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>33.69865028062684</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.355</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.058</v>
+      </c>
+      <c r="AC13" t="n">
         <v>11.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>79.36507936507937</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-8660</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-46.16204690831557</v>
-      </c>
-      <c r="M13" t="n">
-        <v>72.56349206349206</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.287</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.12099</v>
-      </c>
-      <c r="S13" t="n">
-        <v>33.69865028062684</v>
       </c>
     </row>
     <row r="14">
@@ -1347,49 +1863,87 @@
       <c r="E14" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>13.40 - 14.07</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>21.82 - 22.50</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.43103448275862</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9475374732334052</v>
+      </c>
+      <c r="L14" t="n">
         <v>21450.41</v>
       </c>
-      <c r="G14" t="n">
+      <c r="M14" t="n">
         <v>12928.2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="N14" t="n">
+        <v>-8522.210000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-39.72982334603395</v>
+      </c>
+      <c r="P14" t="n">
+        <v>43.95604395604394</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>58.10439560439561</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Wait/Hold</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Keep Holding</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>1.753504815587212</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10.235293</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W14" t="n">
+        <v>15.274</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.16375</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>73.21427507060169</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>21.825</v>
+      </c>
+      <c r="AC14" t="n">
         <v>22.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>43.95604395604394</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-8522.210000000001</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-39.72982334603395</v>
-      </c>
-      <c r="M14" t="n">
-        <v>58.10439560439561</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Wait/Hold</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>10.235293</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>15.274</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.16375</v>
-      </c>
-      <c r="S14" t="n">
-        <v>73.21427507060169</v>
       </c>
     </row>
     <row r="15">
@@ -1412,49 +1966,87 @@
       <c r="E15" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bullish 📈</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8.50 - 8.93</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>9.21 - 9.50</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8.074999999999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1630434782608758</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01333333333333384</v>
+      </c>
+      <c r="L15" t="n">
         <v>8336</v>
       </c>
-      <c r="G15" t="n">
+      <c r="M15" t="n">
         <v>7359.999999999999</v>
       </c>
-      <c r="H15" t="n">
+      <c r="N15" t="n">
+        <v>-976.0000000000009</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-11.70825335892515</v>
+      </c>
+      <c r="P15" t="n">
+        <v>69.99999999999993</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>83</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 8.93</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5044673074319751</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11.219512</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="W15" t="n">
+        <v>20.212</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.925000000000001</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.215</v>
+      </c>
+      <c r="AC15" t="n">
         <v>9.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>69.99999999999993</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-976.0000000000009</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-11.70825335892515</v>
-      </c>
-      <c r="M15" t="n">
-        <v>83</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>11.219512</v>
-      </c>
-      <c r="P15" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>20.212</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.35826</v>
-      </c>
-      <c r="S15" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1477,49 +2069,87 @@
       <c r="E16" t="n">
         <v>6.1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Weak Trend ⚠️</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5.70 - 5.99</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8.34 - 8.60</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.415</v>
+      </c>
+      <c r="J16" t="n">
+        <v>36.75409836065572</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.272992700729928</v>
+      </c>
+      <c r="L16" t="n">
         <v>3714</v>
       </c>
-      <c r="G16" t="n">
+      <c r="M16" t="n">
         <v>3660</v>
       </c>
-      <c r="H16" t="n">
+      <c r="N16" t="n">
+        <v>-54.00000000000045</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1.453957996768994</v>
+      </c>
+      <c r="P16" t="n">
+        <v>13.79310344827585</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>84.12068965517241</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Buy More</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 5.99</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0.8115371921397621</v>
+      </c>
+      <c r="U16" t="n">
+        <v>13.260869</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22.728</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.98037</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>59.6406192386148</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.985</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.341999999999999</v>
+      </c>
+      <c r="AC16" t="n">
         <v>8.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13.79310344827585</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-54.00000000000045</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1.453957996768994</v>
-      </c>
-      <c r="M16" t="n">
-        <v>84.12068965517241</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Buy More</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>13.260869</v>
-      </c>
-      <c r="P16" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>22.728</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.98037</v>
-      </c>
-      <c r="S16" t="n">
-        <v>59.6406192386148</v>
       </c>
     </row>
     <row r="17">
@@ -1542,49 +2172,87 @@
       <c r="E17" t="n">
         <v>16.4</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sideways ➡️</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15.70 - 16.48</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>25.95 - 26.75</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>14.915</v>
+      </c>
+      <c r="J17" t="n">
+        <v>58.21646341463415</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.429292929292932</v>
+      </c>
+      <c r="L17" t="n">
         <v>6559.999999999999</v>
       </c>
-      <c r="G17" t="n">
+      <c r="M17" t="n">
         <v>6559.999999999999</v>
       </c>
-      <c r="H17" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.334841628959269</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>78.36651583710407</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Accumulate</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Buy Now (Good RRR)</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0.2737221410600992</v>
+      </c>
+      <c r="U17" t="n">
+        <v>15.619048</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>14.543</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>48.2758575330645</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>16.485</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.9475</v>
+      </c>
+      <c r="AC17" t="n">
         <v>26.75</v>
-      </c>
-      <c r="I17" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6.334841628959269</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>78.36651583710407</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Accumulate</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>15.619048</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>14.543</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="S17" t="n">
-        <v>48.2758575330645</v>
       </c>
     </row>
     <row r="18">
@@ -1607,49 +2275,87 @@
       <c r="E18" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bearish 📉</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8.25 - 8.66</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>10.67 - 11.00</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7.837499999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17.90055248618783</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.336082474226802</v>
+      </c>
+      <c r="L18" t="n">
         <v>902</v>
       </c>
-      <c r="G18" t="n">
+      <c r="M18" t="n">
         <v>905.0000000000001</v>
       </c>
-      <c r="H18" t="n">
+      <c r="N18" t="n">
+        <v>3.000000000000114</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.3325942350332721</v>
+      </c>
+      <c r="P18" t="n">
+        <v>29.09090909090912</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>83.59090909090909</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Accumulate</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Wait &amp; Bid @ 8.66</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>1.654411764705882</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.6410255</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W18" t="n">
+        <v>11.9160004</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1924</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>25.00005960455951</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8.6625</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AC18" t="n">
         <v>11</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="J18" t="n">
-        <v>29.09090909090912</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.000000000000114</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.3325942350332721</v>
-      </c>
-      <c r="M18" t="n">
-        <v>83.59090909090909</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Accumulate</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>4.6410255</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>11.9160004</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.1924</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25.00005960455951</v>
       </c>
     </row>
   </sheetData>
@@ -1663,7 +2369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1703,51 +2409,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Price_Position</t>
+          <t>Upside_Pct</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ตำแหน่งราคาปัจจุบันเทียบกับรอบ 1 ปี (0 = ต่ำสุด, 100 = สูงสุด)</t>
+          <t>โอกาสกำไร (%) จากราคาปัจจุบันถึงเป้าหมาย</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&lt; 20 = ราคาอยู่โซนล่าง (น่าสนใจ)</t>
+          <t>&gt; 10% = น่าสนใจสะสม</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High_52W / Low_52W</t>
+          <t>RRR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ราคาสูงสุด/ต่ำสุดในรอบ 52 สัปดาห์</t>
+          <t>Risk-Reward Ratio (ความคุ้มค่า)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ใช้ดูแนวรับ-แนวต้านสำคัญ</t>
+          <t>&gt; 2.0 = คุ้มค่าที่จะเสี่ยง</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Advice</t>
+          <t>Target_Action</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>คำแนะนำลงทุน</t>
+          <t>แผนปฏิบัติการระบุราคาและสัดส่วนชัดเจน</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ทำตามระบบ</t>
+          <t>TP = ขายทำกำไร, Reduce = ลดพอร์ต</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stop_Loss</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>จุดตัดขาดทุนเมื่อหลุดแนวรับ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ห้ามถือหุ้นหากราคาหลุดจุดนี้</t>
         </is>
       </c>
     </row>

--- a/portfolio_aom_analysis_report.xlsx
+++ b/portfolio_aom_analysis_report.xlsx
@@ -873,16 +873,16 @@
         <v>14.66666666666669</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.53333333333333</v>
+        <v>71.53333333333333</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Wait/Hold</t>
+          <t>Buy More</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Keep Holding</t>
+          <t>Wait &amp; Bid @ 18.27</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -1079,7 +1079,7 @@
         <v>6.611570247933876</v>
       </c>
       <c r="Q6" t="n">
-        <v>60.33884297520661</v>
+        <v>54.33884297520661</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>29.62962962962964</v>
       </c>
       <c r="Q8" t="n">
-        <v>46.03703703703704</v>
+        <v>52.03703703703704</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45.45454545454543</v>
       </c>
       <c r="Q10" t="n">
-        <v>44.45454545454545</v>
+        <v>38.45454545454545</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>67.49999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>66.75</v>
+        <v>60.75</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>29.09090909090912</v>
       </c>
       <c r="Q18" t="n">
-        <v>83.59090909090909</v>
+        <v>77.59090909090909</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>

--- a/portfolio_aom_analysis_report.xlsx
+++ b/portfolio_aom_analysis_report.xlsx
@@ -1725,7 +1725,7 @@
         <v>0.29902</v>
       </c>
       <c r="Y12" t="n">
-        <v>66.66666666666666</v>
+        <v>66.66663183599771</v>
       </c>
       <c r="Z12" t="n">
         <v>1.15</v>

--- a/portfolio_aom_analysis_report.xlsx
+++ b/portfolio_aom_analysis_report.xlsx
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>0.6505659032171821</v>
+        <v>0.621546133727205</v>
       </c>
       <c r="U2" t="n">
         <v>16</v>
@@ -728,7 +728,7 @@
         <v>6.19</v>
       </c>
       <c r="E3" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
         <v>3.8</v>
       </c>
       <c r="J3" t="n">
-        <v>13.6036036036036</v>
+        <v>14.63636363636363</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4314285714285714</v>
+        <v>0.4735294117647056</v>
       </c>
       <c r="L3" t="n">
         <v>1238</v>
       </c>
       <c r="M3" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="N3" t="n">
-        <v>-128</v>
+        <v>-138</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.33925686591277</v>
+        <v>-11.1470113085622</v>
       </c>
       <c r="P3" t="n">
-        <v>61.99999999999999</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>0.5167883201677864</v>
+        <v>0.4118119677886281</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>1.53247</v>
       </c>
       <c r="Y3" t="n">
-        <v>38.44847539454688</v>
+        <v>39.82405355252289</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
@@ -831,7 +831,7 @@
         <v>20.98</v>
       </c>
       <c r="E4" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -852,28 +852,28 @@
         <v>16.53</v>
       </c>
       <c r="J4" t="n">
-        <v>30.55675675675675</v>
+        <v>31.98360655737704</v>
       </c>
       <c r="K4" t="n">
-        <v>2.869543147208117</v>
+        <v>3.306779661016942</v>
       </c>
       <c r="L4" t="n">
         <v>25176</v>
       </c>
       <c r="M4" t="n">
-        <v>22200</v>
+        <v>21960</v>
       </c>
       <c r="N4" t="n">
-        <v>-2976</v>
+        <v>-3216</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.82078169685415</v>
+        <v>-12.77407054337464</v>
       </c>
       <c r="P4" t="n">
-        <v>14.66666666666669</v>
+        <v>12.00000000000003</v>
       </c>
       <c r="Q4" t="n">
-        <v>71.53333333333333</v>
+        <v>74.8</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>0.7667686188704068</v>
+        <v>0.7932722632351616</v>
       </c>
       <c r="U4" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V4" t="n">
         <v>4.32</v>
@@ -901,7 +901,7 @@
         <v>0.15896</v>
       </c>
       <c r="Y4" t="n">
-        <v>40.00005086250086</v>
+        <v>21.42860062261157</v>
       </c>
       <c r="Z4" t="n">
         <v>17.4</v>
@@ -934,7 +934,7 @@
         <v>57.68</v>
       </c>
       <c r="E5" t="n">
-        <v>44.75</v>
+        <v>44.25</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -955,28 +955,28 @@
         <v>38.475</v>
       </c>
       <c r="J5" t="n">
-        <v>18.13407821229051</v>
+        <v>19.46892655367232</v>
       </c>
       <c r="K5" t="n">
-        <v>1.293227091633467</v>
+        <v>1.491774891774893</v>
       </c>
       <c r="L5" t="n">
         <v>17304</v>
       </c>
       <c r="M5" t="n">
-        <v>13425</v>
+        <v>13275</v>
       </c>
       <c r="N5" t="n">
-        <v>-3879</v>
+        <v>-4029</v>
       </c>
       <c r="O5" t="n">
-        <v>-22.41678224687933</v>
+        <v>-23.28363384188627</v>
       </c>
       <c r="P5" t="n">
-        <v>30.35714285714285</v>
+        <v>26.78571428571428</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.96428571428572</v>
+        <v>58.32142857142857</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>0.6196314228960125</v>
+        <v>0.8964685235269383</v>
       </c>
       <c r="U5" t="n">
-        <v>14.435484</v>
+        <v>14.274194</v>
       </c>
       <c r="V5" t="n">
         <v>3.69</v>
@@ -1004,7 +1004,7 @@
         <v>1.33418</v>
       </c>
       <c r="Y5" t="n">
-        <v>44.82758620689656</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="Z5" t="n">
         <v>40.5</v>
@@ -1037,7 +1037,7 @@
         <v>39.62</v>
       </c>
       <c r="E6" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
         <v>13.205</v>
       </c>
       <c r="J6" t="n">
-        <v>71.56462585034014</v>
+        <v>75.13888888888887</v>
       </c>
       <c r="K6" t="n">
-        <v>7.036789297658866</v>
+        <v>9.054393305439326</v>
       </c>
       <c r="L6" t="n">
         <v>31220.56</v>
       </c>
       <c r="M6" t="n">
-        <v>11583.6</v>
+        <v>11347.2</v>
       </c>
       <c r="N6" t="n">
-        <v>-19636.96</v>
+        <v>-19873.36</v>
       </c>
       <c r="O6" t="n">
-        <v>-62.89752650176679</v>
+        <v>-63.65471983846543</v>
       </c>
       <c r="P6" t="n">
-        <v>6.611570247933876</v>
+        <v>4.132231404958678</v>
       </c>
       <c r="Q6" t="n">
-        <v>54.33884297520661</v>
+        <v>57.58677685950413</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>0.4781806021347391</v>
+        <v>1.152234178563428</v>
       </c>
       <c r="U6" t="n">
-        <v>16.333334</v>
+        <v>16</v>
       </c>
       <c r="V6" t="n">
         <v>8.44</v>
@@ -1107,7 +1107,7 @@
         <v>0.57284</v>
       </c>
       <c r="Y6" t="n">
-        <v>37.92170292856077</v>
+        <v>30.73521214397705</v>
       </c>
       <c r="Z6" t="n">
         <v>13.9</v>
@@ -1140,7 +1140,7 @@
         <v>22.78</v>
       </c>
       <c r="E7" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1161,28 +1161,28 @@
         <v>17.195</v>
       </c>
       <c r="J7" t="n">
-        <v>33.88020833333333</v>
+        <v>35.28947368421051</v>
       </c>
       <c r="K7" t="n">
-        <v>3.244389027431422</v>
+        <v>3.714681440443213</v>
       </c>
       <c r="L7" t="n">
         <v>31892</v>
       </c>
       <c r="M7" t="n">
-        <v>26880</v>
+        <v>26600</v>
       </c>
       <c r="N7" t="n">
-        <v>-5012</v>
+        <v>-5292</v>
       </c>
       <c r="O7" t="n">
-        <v>-15.71553994732222</v>
+        <v>-16.59350307287094</v>
       </c>
       <c r="P7" t="n">
-        <v>13.09523809523807</v>
+        <v>10.7142857142857</v>
       </c>
       <c r="Q7" t="n">
-        <v>65.19047619047619</v>
+        <v>65.42857142857143</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>1.09724800305792</v>
+        <v>1.078992141686298</v>
       </c>
       <c r="U7" t="n">
-        <v>6.1538467</v>
+        <v>6.0897436</v>
       </c>
       <c r="V7" t="n">
         <v>2.6</v>
@@ -1210,7 +1210,7 @@
         <v>2.05188</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.99999694823985</v>
+        <v>14.81480696564016</v>
       </c>
       <c r="Z7" t="n">
         <v>18.1</v>
@@ -1243,7 +1243,7 @@
         <v>32.8</v>
       </c>
       <c r="E8" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1264,28 +1264,28 @@
         <v>15.01</v>
       </c>
       <c r="J8" t="n">
-        <v>31.68010752688171</v>
+        <v>32.39189189189189</v>
       </c>
       <c r="K8" t="n">
-        <v>1.641364902506963</v>
+        <v>1.717048710601719</v>
       </c>
       <c r="L8" t="n">
         <v>3280</v>
       </c>
       <c r="M8" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="N8" t="n">
-        <v>-1419.999999999999</v>
+        <v>-1430</v>
       </c>
       <c r="O8" t="n">
-        <v>-43.29268292682926</v>
+        <v>-43.59756097560975</v>
       </c>
       <c r="P8" t="n">
-        <v>29.62962962962964</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="Q8" t="n">
-        <v>52.03703703703704</v>
+        <v>52.14285714285714</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>0.8269922682385363</v>
+        <v>0.4760718106206246</v>
       </c>
       <c r="U8" t="n">
-        <v>16.607143</v>
+        <v>16.517857</v>
       </c>
       <c r="V8" t="n">
         <v>2.85</v>
@@ -1313,7 +1313,7 @@
         <v>1.54054</v>
       </c>
       <c r="Y8" t="n">
-        <v>64.62050676638384</v>
+        <v>58.02165144864976</v>
       </c>
       <c r="Z8" t="n">
         <v>15.8</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sideways ➡️</t>
+          <t>Weak Trend ⚠️</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>0.4611459049472842</v>
+        <v>0.2828087974125643</v>
       </c>
       <c r="U9" t="n">
         <v>9.347826</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>45.15809304913206</v>
+        <v>39.98342620857609</v>
       </c>
       <c r="Z9" t="n">
         <v>20.8</v>
@@ -1491,7 +1491,7 @@
         <v>45.45454545454543</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.45454545454545</v>
+        <v>42.45454545454545</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>0.5814084071891462</v>
+        <v>1.036380482840065</v>
       </c>
       <c r="U10" t="n">
         <v>12.193548</v>
@@ -1519,7 +1519,7 @@
         <v>1.51037</v>
       </c>
       <c r="Y10" t="n">
-        <v>51.72413793103448</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="Z10" t="n">
         <v>3.18</v>
@@ -1552,7 +1552,7 @@
         <v>21.73</v>
       </c>
       <c r="E11" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,44 +1573,44 @@
         <v>9.594999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>27.15966386554621</v>
+        <v>24.03278688524591</v>
       </c>
       <c r="K11" t="n">
-        <v>1.402169197396962</v>
+        <v>1.12552783109405</v>
       </c>
       <c r="L11" t="n">
         <v>41287</v>
       </c>
       <c r="M11" t="n">
-        <v>22610</v>
+        <v>23180</v>
       </c>
       <c r="N11" t="n">
-        <v>-18677</v>
+        <v>-18107</v>
       </c>
       <c r="O11" t="n">
-        <v>-45.23699953980672</v>
+        <v>-43.85641969627244</v>
       </c>
       <c r="P11" t="n">
-        <v>32.72727272727274</v>
+        <v>38.18181818181818</v>
       </c>
       <c r="Q11" t="n">
-        <v>72.72727272727272</v>
+        <v>69.18181818181819</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Buy More</t>
+          <t>Wait/Hold</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Wait &amp; Bid @ 10.61</t>
+          <t>Keep Holding</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>0.5288999986035275</v>
+        <v>1.574566399645989</v>
       </c>
       <c r="U11" t="n">
-        <v>12.6595745</v>
+        <v>12.978724</v>
       </c>
       <c r="V11" t="n">
         <v>5.04</v>
@@ -1622,7 +1622,7 @@
         <v>0.20703</v>
       </c>
       <c r="Y11" t="n">
-        <v>29.99997456866872</v>
+        <v>39.99998728433436</v>
       </c>
       <c r="Z11" t="n">
         <v>10.1</v>
@@ -1655,11 +1655,11 @@
         <v>2.62</v>
       </c>
       <c r="E12" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish 📈</t>
+          <t>Sideways ➡️</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1676,28 +1676,28 @@
         <v>1.0925</v>
       </c>
       <c r="J12" t="n">
-        <v>5.880281690140855</v>
+        <v>13.04511278195488</v>
       </c>
       <c r="K12" t="n">
-        <v>0.254961832061069</v>
+        <v>0.7305263157894728</v>
       </c>
       <c r="L12" t="n">
         <v>5502</v>
       </c>
       <c r="M12" t="n">
-        <v>2982</v>
+        <v>2793</v>
       </c>
       <c r="N12" t="n">
-        <v>-2520</v>
+        <v>-2709</v>
       </c>
       <c r="O12" t="n">
-        <v>-45.80152671755726</v>
+        <v>-49.23664122137404</v>
       </c>
       <c r="P12" t="n">
-        <v>67.49999999999999</v>
+        <v>45.00000000000002</v>
       </c>
       <c r="Q12" t="n">
-        <v>60.75</v>
+        <v>67</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>2.2144821053118</v>
+        <v>1.42484531917704</v>
       </c>
       <c r="U12" t="n">
-        <v>8.875</v>
+        <v>8.3125</v>
       </c>
       <c r="V12" t="n">
         <v>9.859999999999999</v>
@@ -1725,7 +1725,7 @@
         <v>0.29902</v>
       </c>
       <c r="Y12" t="n">
-        <v>66.66663183599771</v>
+        <v>49.57162688546329</v>
       </c>
       <c r="Z12" t="n">
         <v>1.15</v>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D13" t="n">
-        <v>18.76</v>
+        <v>17.96</v>
       </c>
       <c r="E13" t="n">
-        <v>10.1</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1779,28 +1779,28 @@
         <v>4.845</v>
       </c>
       <c r="J13" t="n">
-        <v>9.485148514851486</v>
+        <v>11.13567839195981</v>
       </c>
       <c r="K13" t="n">
-        <v>0.182302568981922</v>
+        <v>0.2170421155729678</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>19756</v>
       </c>
       <c r="M13" t="n">
-        <v>10100</v>
+        <v>10945</v>
       </c>
       <c r="N13" t="n">
-        <v>-8660</v>
+        <v>-8811</v>
       </c>
       <c r="O13" t="n">
-        <v>-46.16204690831557</v>
+        <v>-44.59910913140313</v>
       </c>
       <c r="P13" t="n">
-        <v>79.36507936507937</v>
+        <v>76.98412698412696</v>
       </c>
       <c r="Q13" t="n">
-        <v>72.56349206349206</v>
+        <v>72.8015873015873</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>0.6275624959835486</v>
+        <v>0.6722730085641206</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0.12099</v>
       </c>
       <c r="Y13" t="n">
-        <v>33.69865028062684</v>
+        <v>34.50211647196622</v>
       </c>
       <c r="Z13" t="n">
         <v>5.1</v>
@@ -1861,7 +1861,7 @@
         <v>28.87</v>
       </c>
       <c r="E14" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1882,28 +1882,28 @@
         <v>12.73</v>
       </c>
       <c r="J14" t="n">
-        <v>25.43103448275862</v>
+        <v>24.71428571428571</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9475374732334052</v>
+        <v>0.9067085953878407</v>
       </c>
       <c r="L14" t="n">
         <v>21450.41</v>
       </c>
       <c r="M14" t="n">
-        <v>12928.2</v>
+        <v>13002.5</v>
       </c>
       <c r="N14" t="n">
-        <v>-8522.210000000001</v>
+        <v>-8447.91</v>
       </c>
       <c r="O14" t="n">
-        <v>-39.72982334603395</v>
+        <v>-39.38344302043645</v>
       </c>
       <c r="P14" t="n">
-        <v>43.95604395604394</v>
+        <v>45.05494505494505</v>
       </c>
       <c r="Q14" t="n">
-        <v>58.10439560439561</v>
+        <v>60.9945054945055</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>1.753504815587212</v>
+        <v>0.7262332566181172</v>
       </c>
       <c r="U14" t="n">
-        <v>10.235293</v>
+        <v>10.294117</v>
       </c>
       <c r="V14" t="n">
         <v>1.95</v>
@@ -1931,7 +1931,7 @@
         <v>2.16375</v>
       </c>
       <c r="Y14" t="n">
-        <v>73.21427507060169</v>
+        <v>69.99999237060838</v>
       </c>
       <c r="Z14" t="n">
         <v>13.4</v>
@@ -1964,11 +1964,11 @@
         <v>10.42</v>
       </c>
       <c r="E15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish 📈</t>
+          <t>Weak Trend ⚠️</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1985,28 +1985,28 @@
         <v>8.074999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1630434782608758</v>
+        <v>0.7103825136611968</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01333333333333384</v>
+        <v>0.06046511627906925</v>
       </c>
       <c r="L15" t="n">
         <v>8336</v>
       </c>
       <c r="M15" t="n">
-        <v>7359.999999999999</v>
+        <v>7320</v>
       </c>
       <c r="N15" t="n">
-        <v>-976.0000000000009</v>
+        <v>-1016</v>
       </c>
       <c r="O15" t="n">
-        <v>-11.70825335892515</v>
+        <v>-12.18809980806142</v>
       </c>
       <c r="P15" t="n">
-        <v>69.99999999999993</v>
+        <v>65.00000000000003</v>
       </c>
       <c r="Q15" t="n">
-        <v>83</v>
+        <v>87.5</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>0.5044673074319751</v>
+        <v>1.786347740630387</v>
       </c>
       <c r="U15" t="n">
-        <v>11.219512</v>
+        <v>11.158536</v>
       </c>
       <c r="V15" t="n">
         <v>6.52</v>
@@ -2034,7 +2034,7 @@
         <v>0.35826</v>
       </c>
       <c r="Y15" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Z15" t="n">
         <v>8.5</v>
@@ -2067,11 +2067,11 @@
         <v>6.19</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Weak Trend ⚠️</t>
+          <t>Sideways ➡️</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2088,28 +2088,28 @@
         <v>5.415</v>
       </c>
       <c r="J16" t="n">
-        <v>36.75409836065572</v>
+        <v>37.88429752066114</v>
       </c>
       <c r="K16" t="n">
-        <v>3.272992700729928</v>
+        <v>3.609448818897637</v>
       </c>
       <c r="L16" t="n">
         <v>3714</v>
       </c>
       <c r="M16" t="n">
-        <v>3660</v>
+        <v>3630</v>
       </c>
       <c r="N16" t="n">
-        <v>-54.00000000000045</v>
+        <v>-84.00000000000045</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.453957996768994</v>
+        <v>-2.261712439418426</v>
       </c>
       <c r="P16" t="n">
-        <v>13.79310344827585</v>
+        <v>12.06896551724137</v>
       </c>
       <c r="Q16" t="n">
-        <v>84.12068965517241</v>
+        <v>88.29310344827587</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>0.8115371921397621</v>
+        <v>0.3800433115194043</v>
       </c>
       <c r="U16" t="n">
-        <v>13.260869</v>
+        <v>13.152174</v>
       </c>
       <c r="V16" t="n">
         <v>7.21</v>
@@ -2137,7 +2137,7 @@
         <v>0.98037</v>
       </c>
       <c r="Y16" t="n">
-        <v>59.6406192386148</v>
+        <v>47.88718889795504</v>
       </c>
       <c r="Z16" t="n">
         <v>5.7</v>
@@ -2164,17 +2164,17 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D17" t="n">
-        <v>16.4</v>
+        <v>16.49</v>
       </c>
       <c r="E17" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sideways ➡️</t>
+          <t>Bearish 📉</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2191,32 +2191,32 @@
         <v>14.915</v>
       </c>
       <c r="J17" t="n">
-        <v>58.21646341463415</v>
+        <v>59.18711656441717</v>
       </c>
       <c r="K17" t="n">
-        <v>6.429292929292932</v>
+        <v>6.965703971119124</v>
       </c>
       <c r="L17" t="n">
-        <v>6559.999999999999</v>
+        <v>8245</v>
       </c>
       <c r="M17" t="n">
-        <v>6559.999999999999</v>
+        <v>8150</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-95</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.152213462704656</v>
       </c>
       <c r="P17" t="n">
-        <v>6.334841628959269</v>
+        <v>5.429864253393678</v>
       </c>
       <c r="Q17" t="n">
-        <v>78.36651583710407</v>
+        <v>78.45701357466064</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Accumulate</t>
+          <t>Buy More</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>0.2737221410600992</v>
+        <v>0.5936901199464901</v>
       </c>
       <c r="U17" t="n">
-        <v>15.619048</v>
+        <v>15.523809</v>
       </c>
       <c r="V17" t="n">
         <v>3.05</v>
@@ -2240,7 +2240,7 @@
         <v>0.272</v>
       </c>
       <c r="Y17" t="n">
-        <v>48.2758575330645</v>
+        <v>38.46154974760683</v>
       </c>
       <c r="Z17" t="n">
         <v>15.7</v>
@@ -2273,7 +2273,7 @@
         <v>9.02</v>
       </c>
       <c r="E18" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2294,32 +2294,32 @@
         <v>7.837499999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>17.90055248618783</v>
+        <v>19.21787709497207</v>
       </c>
       <c r="K18" t="n">
-        <v>1.336082474226802</v>
+        <v>1.546067415730338</v>
       </c>
       <c r="L18" t="n">
         <v>902</v>
       </c>
       <c r="M18" t="n">
-        <v>905.0000000000001</v>
+        <v>894.9999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>3.000000000000114</v>
+        <v>-7.000000000000114</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3325942350332721</v>
+        <v>-0.7760532150776085</v>
       </c>
       <c r="P18" t="n">
-        <v>29.09090909090912</v>
+        <v>25.45454545454543</v>
       </c>
       <c r="Q18" t="n">
-        <v>77.59090909090909</v>
+        <v>77.95454545454545</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Accumulate</t>
+          <t>Buy More</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>1.654411764705882</v>
+        <v>1.094218157988333</v>
       </c>
       <c r="U18" t="n">
-        <v>4.6410255</v>
+        <v>4.5897436</v>
       </c>
       <c r="V18" t="n">
         <v>2.21</v>
@@ -2343,7 +2343,7 @@
         <v>0.1924</v>
       </c>
       <c r="Y18" t="n">
-        <v>25.00005960455951</v>
+        <v>22.22226931717034</v>
       </c>
       <c r="Z18" t="n">
         <v>8.25</v>
